--- a/Spinning.xlsx
+++ b/Spinning.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nikhitha\OneDrive\Desktop\Manning_AUM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{973EC5F6-0503-4876-A641-B27B31A60042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A27A5A94-B1FD-49F2-9F70-8465DE6A863E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Spinning" sheetId="1" r:id="rId1"/>
@@ -35,15 +35,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="286">
   <si>
     <t>Location</t>
   </si>
   <si>
     <t>Business</t>
-  </si>
-  <si>
-    <t>Department</t>
   </si>
   <si>
     <t>Sr_No</t>
@@ -961,6 +958,36 @@
   </cellStyles>
   <dxfs count="31">
     <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -1016,36 +1043,6 @@
         <scheme val="minor"/>
       </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
       <font>
@@ -1384,16 +1381,16 @@
     <tableColumn id="9" xr3:uid="{090D3B71-C4CF-432F-B817-104F30316591}" name="Workload" dataDxfId="22"/>
     <tableColumn id="10" xr3:uid="{9EDB9484-B177-478C-9BA3-4C1AE3030F95}" name="Formulas" dataDxfId="21"/>
     <tableColumn id="11" xr3:uid="{3A1186F6-9294-4AEC-A543-A07372ADEF4D}" name="BE_Scientific_Manpower" dataDxfId="20"/>
-    <tableColumn id="20" xr3:uid="{071CCBE0-65D5-467E-AFCC-8949549E1BB6}" name="Operator_Type" dataDxfId="0"/>
-    <tableColumn id="8" xr3:uid="{F5544431-B0F5-4C79-B5EB-61614939F4B5}" name="Contractors" dataDxfId="2"/>
-    <tableColumn id="19" xr3:uid="{15BE4AF0-E211-4DE0-800A-0EDB9C705B37}" name="Company_Associate" dataDxfId="1"/>
-    <tableColumn id="12" xr3:uid="{47E45710-4EB9-4699-B8AD-09AC38DE8C54}" name="BE_Final_Manpower" dataDxfId="19"/>
-    <tableColumn id="13" xr3:uid="{38203A5B-662C-436E-A752-C238B552EF03}" name="General_Shift" dataDxfId="18"/>
-    <tableColumn id="14" xr3:uid="{3D149A8F-3122-4C7E-B50D-02B6DF1691E0}" name="Shift_A" dataDxfId="17"/>
-    <tableColumn id="15" xr3:uid="{0AFA7034-EEDB-4D14-A601-C01016D3A7D5}" name="Shift_B" dataDxfId="16"/>
-    <tableColumn id="16" xr3:uid="{64D43A66-597F-4C18-84E0-E76FCB0F95CC}" name="Shift_C" dataDxfId="15"/>
-    <tableColumn id="17" xr3:uid="{554EDC51-4B6D-44FF-BB2C-DA6797B32110}" name="Reliever" dataDxfId="14"/>
-    <tableColumn id="18" xr3:uid="{FF4E975E-F83C-4D1D-8950-072C414D6E58}" name="Remarks" dataDxfId="13"/>
+    <tableColumn id="20" xr3:uid="{071CCBE0-65D5-467E-AFCC-8949549E1BB6}" name="Operator_Type" dataDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{F5544431-B0F5-4C79-B5EB-61614939F4B5}" name="Contractors" dataDxfId="18"/>
+    <tableColumn id="19" xr3:uid="{15BE4AF0-E211-4DE0-800A-0EDB9C705B37}" name="Company_Associate" dataDxfId="17"/>
+    <tableColumn id="12" xr3:uid="{47E45710-4EB9-4699-B8AD-09AC38DE8C54}" name="BE_Final_Manpower" dataDxfId="16"/>
+    <tableColumn id="13" xr3:uid="{38203A5B-662C-436E-A752-C238B552EF03}" name="General_Shift" dataDxfId="15"/>
+    <tableColumn id="14" xr3:uid="{3D149A8F-3122-4C7E-B50D-02B6DF1691E0}" name="Shift_A" dataDxfId="14"/>
+    <tableColumn id="15" xr3:uid="{0AFA7034-EEDB-4D14-A601-C01016D3A7D5}" name="Shift_B" dataDxfId="13"/>
+    <tableColumn id="16" xr3:uid="{64D43A66-597F-4C18-84E0-E76FCB0F95CC}" name="Shift_C" dataDxfId="12"/>
+    <tableColumn id="17" xr3:uid="{554EDC51-4B6D-44FF-BB2C-DA6797B32110}" name="Reliever" dataDxfId="11"/>
+    <tableColumn id="18" xr3:uid="{FF4E975E-F83C-4D1D-8950-072C414D6E58}" name="Remarks" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1424,18 +1421,18 @@
       <calculatedColumnFormula>L2/I2</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="13" xr3:uid="{7C882653-B2FB-4460-945F-BEC827034FAE}" name="formula_No. of TFO Required/ shift "/>
-    <tableColumn id="14" xr3:uid="{74DD064C-08DB-4132-A242-1290AD15CDB8}" name="No. of TFO Required/ shift " dataDxfId="12" totalsRowDxfId="11"/>
+    <tableColumn id="14" xr3:uid="{74DD064C-08DB-4132-A242-1290AD15CDB8}" name="No. of TFO Required/ shift " dataDxfId="9" totalsRowDxfId="8"/>
     <tableColumn id="15" xr3:uid="{65F3003E-C476-4D6D-BE1A-6488E17CDB9D}" name="mpm"/>
-    <tableColumn id="16" xr3:uid="{6E9D763E-DE2C-4A86-B1EA-5287AC19467B}" name="Eff" dataDxfId="10" totalsRowDxfId="9"/>
-    <tableColumn id="17" xr3:uid="{4C4EE216-BFC8-45EA-BA92-DA7C3E734438}" name="Formula_kgs/drum/day " dataDxfId="8" totalsRowDxfId="7"/>
+    <tableColumn id="16" xr3:uid="{6E9D763E-DE2C-4A86-B1EA-5287AC19467B}" name="Eff" dataDxfId="7" totalsRowDxfId="6"/>
+    <tableColumn id="17" xr3:uid="{4C4EE216-BFC8-45EA-BA92-DA7C3E734438}" name="Formula_kgs/drum/day " dataDxfId="5" totalsRowDxfId="4"/>
     <tableColumn id="18" xr3:uid="{00170897-62B8-4C84-AE04-5EAE44ABC362}" name="kgs/drum/day ">
       <calculatedColumnFormula>Q2*R2*8*60*1.09/(C2*840*2.202)*3</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="19" xr3:uid="{2DD7DB04-94B4-4773-9E4C-D99D0E582A8C}" name="formula_No. of Drums"/>
-    <tableColumn id="20" xr3:uid="{B964DFB3-EA94-419A-8A86-F1F5917ADCA3}" name="No. of Drums " dataDxfId="6" totalsRowDxfId="5">
+    <tableColumn id="20" xr3:uid="{B964DFB3-EA94-419A-8A86-F1F5917ADCA3}" name="No. of Drums " dataDxfId="3" totalsRowDxfId="2">
       <calculatedColumnFormula>L2/T2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{ACA15BF8-B0A7-481E-A7F2-D7E94E5D9CB0}" name="formula_no. of machines" dataDxfId="4" totalsRowDxfId="3"/>
+    <tableColumn id="21" xr3:uid="{ACA15BF8-B0A7-481E-A7F2-D7E94E5D9CB0}" name="formula_no. of machines" dataDxfId="1" totalsRowDxfId="0"/>
     <tableColumn id="22" xr3:uid="{0459E32F-2AB6-434A-9439-F5F08B7C6254}" name="no. of machines">
       <calculatedColumnFormula>V2/72</calculatedColumnFormula>
     </tableColumn>
@@ -1757,87 +1754,87 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>286</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J1" t="s">
+        <v>270</v>
+      </c>
+      <c r="K1" t="s">
+        <v>284</v>
+      </c>
+      <c r="L1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1" t="s">
+        <v>283</v>
+      </c>
+      <c r="N1" t="s">
+        <v>269</v>
+      </c>
+      <c r="O1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I1" t="s">
-        <v>46</v>
-      </c>
-      <c r="J1" t="s">
-        <v>271</v>
-      </c>
-      <c r="K1" t="s">
-        <v>285</v>
-      </c>
-      <c r="L1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M1" t="s">
-        <v>284</v>
-      </c>
-      <c r="N1" t="s">
-        <v>270</v>
-      </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>6</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>7</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>8</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>9</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>10</v>
-      </c>
-      <c r="T1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
         <v>14</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2" t="s">
-        <v>15</v>
-      </c>
       <c r="F2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G2">
         <v>8</v>
       </c>
       <c r="H2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J2">
         <v>12</v>
@@ -1861,36 +1858,36 @@
         <v>0</v>
       </c>
       <c r="T2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
       <c r="D3">
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G3">
         <v>52</v>
       </c>
       <c r="H3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J3">
         <v>7.09</v>
@@ -1916,31 +1913,31 @@
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
         <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
       </c>
       <c r="D4">
         <v>3</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G4">
         <v>9</v>
       </c>
       <c r="H4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J4">
         <v>3</v>
@@ -1966,31 +1963,31 @@
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
         <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
       </c>
       <c r="D5">
         <v>4</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G5">
         <v>22</v>
       </c>
       <c r="H5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J5">
         <v>16.5</v>
@@ -2016,31 +2013,31 @@
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
         <v>13</v>
-      </c>
-      <c r="C6" t="s">
-        <v>14</v>
       </c>
       <c r="D6">
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G6">
         <v>4</v>
       </c>
       <c r="H6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J6">
         <v>3</v>
@@ -2066,31 +2063,31 @@
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
         <v>13</v>
-      </c>
-      <c r="C7" t="s">
-        <v>14</v>
       </c>
       <c r="D7">
         <v>6</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G7">
         <v>3</v>
       </c>
       <c r="H7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J7">
         <v>4.5</v>
@@ -2116,31 +2113,31 @@
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
         <v>13</v>
-      </c>
-      <c r="C8" t="s">
-        <v>14</v>
       </c>
       <c r="D8">
         <v>7</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G8">
         <v>18</v>
       </c>
       <c r="H8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J8">
         <v>5.4</v>
@@ -2166,31 +2163,31 @@
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
         <v>13</v>
-      </c>
-      <c r="C9" t="s">
-        <v>14</v>
       </c>
       <c r="D9">
         <v>8</v>
       </c>
       <c r="E9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G9">
         <v>21</v>
       </c>
       <c r="H9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J9">
         <v>15.75</v>
@@ -2216,31 +2213,31 @@
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" t="s">
         <v>13</v>
-      </c>
-      <c r="C10" t="s">
-        <v>14</v>
       </c>
       <c r="D10">
         <v>9</v>
       </c>
       <c r="E10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G10">
         <v>5</v>
       </c>
       <c r="H10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J10">
         <v>3.75</v>
@@ -2266,31 +2263,31 @@
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" t="s">
         <v>13</v>
-      </c>
-      <c r="C11" t="s">
-        <v>14</v>
       </c>
       <c r="D11">
         <v>10</v>
       </c>
       <c r="E11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G11">
         <v>16</v>
       </c>
       <c r="H11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J11">
         <v>24</v>
@@ -2314,36 +2311,36 @@
         <v>0</v>
       </c>
       <c r="T11" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" t="s">
         <v>13</v>
       </c>
-      <c r="C12" t="s">
-        <v>14</v>
-      </c>
       <c r="D12">
         <v>11</v>
       </c>
       <c r="E12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" t="s">
         <v>26</v>
-      </c>
-      <c r="F12" t="s">
-        <v>27</v>
       </c>
       <c r="G12">
         <v>16</v>
       </c>
       <c r="H12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J12">
         <v>24</v>
@@ -2369,28 +2366,28 @@
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
         <v>13</v>
       </c>
-      <c r="C13" t="s">
-        <v>14</v>
-      </c>
       <c r="D13">
         <v>12</v>
       </c>
       <c r="E13" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" t="s">
         <v>28</v>
       </c>
-      <c r="F13" t="s">
-        <v>29</v>
-      </c>
       <c r="H13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J13">
         <v>3</v>
@@ -2416,28 +2413,28 @@
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" t="s">
         <v>13</v>
-      </c>
-      <c r="C14" t="s">
-        <v>14</v>
       </c>
       <c r="D14">
         <v>13</v>
       </c>
       <c r="E14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I14" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J14">
         <v>6</v>
@@ -2463,28 +2460,28 @@
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" t="s">
         <v>13</v>
-      </c>
-      <c r="C15" t="s">
-        <v>14</v>
       </c>
       <c r="D15">
         <v>14</v>
       </c>
       <c r="E15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F15" t="s">
         <v>31</v>
       </c>
-      <c r="F15" t="s">
-        <v>32</v>
-      </c>
       <c r="H15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J15">
         <v>6</v>
@@ -2510,28 +2507,28 @@
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" t="s">
         <v>13</v>
-      </c>
-      <c r="C16" t="s">
-        <v>14</v>
       </c>
       <c r="D16">
         <v>15</v>
       </c>
       <c r="E16" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I16" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2555,36 +2552,36 @@
         <v>0</v>
       </c>
       <c r="T16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C17" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17" t="s">
         <v>58</v>
       </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-      <c r="E17" t="s">
-        <v>59</v>
-      </c>
       <c r="F17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G17">
         <v>7</v>
       </c>
       <c r="H17" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J17">
         <v>30</v>
@@ -2610,31 +2607,31 @@
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C18" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D18">
         <v>2</v>
       </c>
       <c r="E18" t="s">
+        <v>60</v>
+      </c>
+      <c r="F18" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18">
+        <v>12</v>
+      </c>
+      <c r="H18" t="s">
+        <v>98</v>
+      </c>
+      <c r="I18" t="s">
         <v>61</v>
-      </c>
-      <c r="F18" t="s">
-        <v>16</v>
-      </c>
-      <c r="G18">
-        <v>12</v>
-      </c>
-      <c r="H18" t="s">
-        <v>99</v>
-      </c>
-      <c r="I18" t="s">
-        <v>62</v>
       </c>
       <c r="J18">
         <v>25</v>
@@ -2660,31 +2657,31 @@
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D19">
         <v>3</v>
       </c>
       <c r="E19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G19">
         <v>18</v>
       </c>
       <c r="H19" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J19">
         <v>54</v>
@@ -2710,31 +2707,31 @@
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C20" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D20">
         <v>4</v>
       </c>
       <c r="E20" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G20">
         <v>4</v>
       </c>
       <c r="H20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I20" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J20">
         <v>12</v>
@@ -2760,28 +2757,28 @@
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D21">
         <v>5</v>
       </c>
       <c r="E21" t="s">
+        <v>66</v>
+      </c>
+      <c r="F21" t="s">
+        <v>15</v>
+      </c>
+      <c r="H21" t="s">
         <v>67</v>
       </c>
-      <c r="F21" t="s">
-        <v>16</v>
-      </c>
-      <c r="H21" t="s">
+      <c r="I21" t="s">
         <v>68</v>
-      </c>
-      <c r="I21" t="s">
-        <v>69</v>
       </c>
       <c r="J21">
         <v>18</v>
@@ -2807,31 +2804,31 @@
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C22" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D22">
         <v>6</v>
       </c>
       <c r="E22" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G22">
         <v>52608</v>
       </c>
       <c r="H22" t="s">
+        <v>70</v>
+      </c>
+      <c r="I22" t="s">
         <v>71</v>
-      </c>
-      <c r="I22" t="s">
-        <v>72</v>
       </c>
       <c r="J22">
         <v>41</v>
@@ -2857,31 +2854,31 @@
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D23">
         <v>7</v>
       </c>
       <c r="E23" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G23">
         <v>7</v>
       </c>
       <c r="H23" t="s">
+        <v>73</v>
+      </c>
+      <c r="I23" t="s">
         <v>74</v>
-      </c>
-      <c r="I23" t="s">
-        <v>75</v>
       </c>
       <c r="J23">
         <v>6</v>
@@ -2907,31 +2904,31 @@
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C24" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D24">
         <v>8</v>
       </c>
       <c r="E24" t="s">
+        <v>75</v>
+      </c>
+      <c r="F24" t="s">
+        <v>15</v>
+      </c>
+      <c r="G24">
+        <v>12</v>
+      </c>
+      <c r="H24" t="s">
         <v>76</v>
       </c>
-      <c r="F24" t="s">
-        <v>16</v>
-      </c>
-      <c r="G24">
-        <v>12</v>
-      </c>
-      <c r="H24" t="s">
+      <c r="I24" t="s">
         <v>77</v>
-      </c>
-      <c r="I24" t="s">
-        <v>78</v>
       </c>
       <c r="J24">
         <v>6</v>
@@ -2957,31 +2954,31 @@
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D25">
         <v>9</v>
       </c>
       <c r="E25" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G25">
         <v>18</v>
       </c>
       <c r="H25" t="s">
+        <v>79</v>
+      </c>
+      <c r="I25" t="s">
         <v>80</v>
-      </c>
-      <c r="I25" t="s">
-        <v>81</v>
       </c>
       <c r="J25">
         <v>12</v>
@@ -3007,31 +3004,31 @@
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C26" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D26">
         <v>10</v>
       </c>
       <c r="E26" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G26">
         <v>4</v>
       </c>
       <c r="H26" t="s">
+        <v>82</v>
+      </c>
+      <c r="I26" t="s">
         <v>83</v>
-      </c>
-      <c r="I26" t="s">
-        <v>84</v>
       </c>
       <c r="J26">
         <v>3</v>
@@ -3057,25 +3054,25 @@
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C27" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D27">
         <v>11</v>
       </c>
       <c r="E27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F27" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I27" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J27">
         <v>9</v>
@@ -3099,33 +3096,33 @@
         <v>0</v>
       </c>
       <c r="T27" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C28" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D28">
         <v>12</v>
       </c>
       <c r="E28" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G28">
         <v>52608</v>
       </c>
       <c r="I28" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J28">
         <v>6</v>
@@ -3149,30 +3146,30 @@
         <v>0</v>
       </c>
       <c r="T28" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C29" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D29">
         <v>13</v>
       </c>
       <c r="E29" t="s">
+        <v>87</v>
+      </c>
+      <c r="F29" t="s">
         <v>88</v>
       </c>
-      <c r="F29" t="s">
-        <v>89</v>
-      </c>
       <c r="I29" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J29">
         <v>6</v>
@@ -3196,30 +3193,30 @@
         <v>0</v>
       </c>
       <c r="T29" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C30" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D30">
         <v>14</v>
       </c>
       <c r="E30" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F30" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I30" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J30">
         <v>6</v>
@@ -3243,30 +3240,30 @@
         <v>0</v>
       </c>
       <c r="T30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C31" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D31">
         <v>15</v>
       </c>
       <c r="E31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F31" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I31" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J31">
         <v>6</v>
@@ -3290,30 +3287,30 @@
         <v>0</v>
       </c>
       <c r="T31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C32" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D32">
         <v>16</v>
       </c>
       <c r="E32" t="s">
+        <v>91</v>
+      </c>
+      <c r="H32" t="s">
         <v>92</v>
       </c>
-      <c r="H32" t="s">
-        <v>93</v>
-      </c>
       <c r="I32" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J32">
         <v>6</v>
@@ -3337,30 +3334,30 @@
         <v>0</v>
       </c>
       <c r="T32" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C33" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D33">
         <v>17</v>
       </c>
       <c r="E33" t="s">
+        <v>93</v>
+      </c>
+      <c r="H33" t="s">
         <v>94</v>
       </c>
-      <c r="H33" t="s">
-        <v>95</v>
-      </c>
       <c r="I33" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J33">
         <v>6</v>
@@ -3384,30 +3381,30 @@
         <v>0</v>
       </c>
       <c r="T33" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C34" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D34">
         <v>18</v>
       </c>
       <c r="E34" t="s">
+        <v>95</v>
+      </c>
+      <c r="H34" t="s">
         <v>96</v>
       </c>
-      <c r="H34" t="s">
-        <v>97</v>
-      </c>
       <c r="I34" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J34">
         <v>6</v>
@@ -3431,30 +3428,30 @@
         <v>0</v>
       </c>
       <c r="T34" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D35">
         <v>19</v>
       </c>
       <c r="E35" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F35" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I35" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J35">
         <v>12</v>
@@ -3480,28 +3477,28 @@
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C36" t="s">
+        <v>100</v>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="E36" t="s">
         <v>101</v>
-      </c>
-      <c r="D36">
-        <v>1</v>
-      </c>
-      <c r="E36" t="s">
-        <v>102</v>
       </c>
       <c r="G36">
         <v>29</v>
       </c>
       <c r="H36" t="s">
+        <v>102</v>
+      </c>
+      <c r="I36" t="s">
         <v>103</v>
-      </c>
-      <c r="I36" t="s">
-        <v>104</v>
       </c>
       <c r="J36">
         <v>22</v>
@@ -3527,28 +3524,28 @@
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B37" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C37" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D37">
         <v>2</v>
       </c>
       <c r="E37" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G37">
         <v>6</v>
       </c>
       <c r="H37" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="I37" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J37">
         <v>30</v>
@@ -3574,22 +3571,22 @@
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B38" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D38">
         <v>3</v>
       </c>
       <c r="E38" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I38" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J38">
         <v>6</v>
@@ -3613,27 +3610,27 @@
         <v>0</v>
       </c>
       <c r="T38" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C39" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D39">
         <v>4</v>
       </c>
       <c r="E39" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I39" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J39">
         <v>6</v>
@@ -3657,30 +3654,30 @@
         <v>0</v>
       </c>
       <c r="T39" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B40" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C40" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D40">
         <v>5</v>
       </c>
       <c r="E40" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F40" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I40" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J40">
         <v>3</v>
@@ -3704,30 +3701,30 @@
         <v>0</v>
       </c>
       <c r="T40" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B41" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C41" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D41">
         <v>6</v>
       </c>
       <c r="E41" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F41" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I41" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J41">
         <v>1</v>
@@ -3751,30 +3748,30 @@
         <v>0</v>
       </c>
       <c r="T41" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C42" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D42">
         <v>7</v>
       </c>
       <c r="E42" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F42" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I42" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J42">
         <v>3</v>
@@ -3798,30 +3795,30 @@
         <v>0</v>
       </c>
       <c r="T42" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B43" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C43" t="s">
+        <v>108</v>
+      </c>
+      <c r="D43">
+        <v>1</v>
+      </c>
+      <c r="E43" t="s">
         <v>109</v>
       </c>
-      <c r="D43">
-        <v>1</v>
-      </c>
-      <c r="E43" t="s">
-        <v>110</v>
-      </c>
       <c r="F43" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I43" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J43">
         <v>3</v>
@@ -3845,30 +3842,30 @@
         <v>0</v>
       </c>
       <c r="T43" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B44" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C44" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D44">
         <v>2</v>
       </c>
       <c r="E44" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F44" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I44" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J44">
         <v>0</v>
@@ -3892,30 +3889,30 @@
         <v>0</v>
       </c>
       <c r="T44" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B45" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C45" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D45">
         <v>3</v>
       </c>
       <c r="E45" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F45" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I45" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J45">
         <v>3</v>
@@ -3939,33 +3936,33 @@
         <v>0</v>
       </c>
       <c r="T45" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B46" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C46" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D46">
         <v>4</v>
       </c>
       <c r="E46" t="s">
+        <v>112</v>
+      </c>
+      <c r="F46" t="s">
+        <v>112</v>
+      </c>
+      <c r="H46" t="s">
         <v>113</v>
       </c>
-      <c r="F46" t="s">
-        <v>113</v>
-      </c>
-      <c r="H46" t="s">
-        <v>114</v>
-      </c>
       <c r="I46" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J46">
         <v>6</v>
@@ -3989,33 +3986,33 @@
         <v>0</v>
       </c>
       <c r="T46" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B47" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C47" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D47">
         <v>5</v>
       </c>
       <c r="E47" t="s">
+        <v>114</v>
+      </c>
+      <c r="F47" t="s">
         <v>115</v>
       </c>
-      <c r="F47" t="s">
+      <c r="H47" t="s">
         <v>116</v>
       </c>
-      <c r="H47" t="s">
-        <v>117</v>
-      </c>
       <c r="I47" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J47">
         <v>3</v>
@@ -4039,36 +4036,36 @@
         <v>0</v>
       </c>
       <c r="T47" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B48" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C48" t="s">
+        <v>117</v>
+      </c>
+      <c r="D48">
+        <v>1</v>
+      </c>
+      <c r="E48" t="s">
         <v>118</v>
       </c>
-      <c r="D48">
-        <v>1</v>
-      </c>
-      <c r="E48" t="s">
+      <c r="F48" t="s">
         <v>119</v>
-      </c>
-      <c r="F48" t="s">
-        <v>120</v>
       </c>
       <c r="G48">
         <v>8</v>
       </c>
       <c r="H48" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I48" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J48">
         <v>24</v>
@@ -4094,25 +4091,25 @@
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B49" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C49" t="s">
+        <v>117</v>
+      </c>
+      <c r="D49">
+        <v>2</v>
+      </c>
+      <c r="E49" t="s">
         <v>118</v>
       </c>
-      <c r="D49">
-        <v>2</v>
-      </c>
-      <c r="E49" t="s">
-        <v>119</v>
-      </c>
       <c r="F49" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I49" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J49">
         <v>3</v>
@@ -4138,25 +4135,25 @@
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B50" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C50" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D50">
         <v>3</v>
       </c>
       <c r="E50" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F50" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I50" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J50">
         <v>1</v>
@@ -4182,25 +4179,25 @@
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D51" s="4">
         <v>1</v>
       </c>
       <c r="E51" s="4"/>
       <c r="F51" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
       <c r="I51" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="J51" s="4">
         <v>14</v>
@@ -4230,25 +4227,25 @@
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D52" s="4">
         <v>2</v>
       </c>
       <c r="E52" s="4"/>
       <c r="F52" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
       <c r="I52" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="J52" s="4">
         <v>6</v>
@@ -4278,25 +4275,25 @@
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D53" s="4">
         <v>3</v>
       </c>
       <c r="E53" s="4"/>
       <c r="F53" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
       <c r="I53" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="J53" s="4">
         <v>6</v>
@@ -4326,25 +4323,25 @@
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D54" s="1">
         <v>4</v>
       </c>
       <c r="E54" s="1"/>
       <c r="F54" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
       <c r="I54" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J54" s="1">
         <v>1</v>
@@ -4374,27 +4371,27 @@
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D55" s="1">
         <v>1</v>
       </c>
       <c r="E55" s="1"/>
       <c r="F55" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G55" s="1"/>
       <c r="H55" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J55" s="1">
         <v>12</v>
@@ -4424,27 +4421,27 @@
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D56" s="1">
         <v>2</v>
       </c>
       <c r="E56" s="1"/>
       <c r="F56" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G56" s="1"/>
       <c r="H56" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="I56" s="1" t="s">
         <v>147</v>
-      </c>
-      <c r="I56" s="1" t="s">
-        <v>148</v>
       </c>
       <c r="J56" s="1">
         <v>6</v>
@@ -4474,27 +4471,27 @@
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D57" s="1">
         <v>3</v>
       </c>
       <c r="E57" s="1"/>
       <c r="F57" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G57" s="1"/>
       <c r="H57" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J57" s="1">
         <v>2</v>
@@ -4524,27 +4521,27 @@
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D58" s="1">
         <v>4</v>
       </c>
       <c r="E58" s="1"/>
       <c r="F58" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G58" s="1"/>
       <c r="H58" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J58" s="1">
         <v>12</v>
@@ -4571,32 +4568,32 @@
         <v>0</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D59" s="1">
         <v>1</v>
       </c>
       <c r="E59" s="1"/>
       <c r="F59" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G59" s="1"/>
       <c r="H59" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="I59" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="I59" s="1" t="s">
-        <v>156</v>
       </c>
       <c r="J59" s="1">
         <v>3</v>
@@ -4626,27 +4623,27 @@
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D60" s="1">
         <v>2</v>
       </c>
       <c r="E60" s="1"/>
       <c r="F60" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G60" s="1"/>
       <c r="H60" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J60" s="1">
         <v>1</v>
@@ -4676,27 +4673,27 @@
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D61" s="1">
         <v>3</v>
       </c>
       <c r="E61" s="1"/>
       <c r="F61" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G61" s="1"/>
       <c r="H61" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J61" s="1">
         <v>3</v>
@@ -4726,27 +4723,27 @@
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D62" s="1">
         <v>4</v>
       </c>
       <c r="E62" s="1"/>
       <c r="F62" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G62" s="1"/>
       <c r="H62" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J62" s="1">
         <v>3</v>
@@ -4773,32 +4770,32 @@
         <v>0</v>
       </c>
       <c r="T62" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D63" s="1">
         <v>5</v>
       </c>
       <c r="E63" s="1"/>
       <c r="F63" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G63" s="1"/>
       <c r="H63" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J63" s="1">
         <v>12</v>
@@ -4828,27 +4825,27 @@
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D64" s="1">
         <v>1</v>
       </c>
       <c r="E64" s="1"/>
       <c r="F64" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G64" s="1"/>
       <c r="H64" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="I64" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="I64" s="1" t="s">
-        <v>156</v>
       </c>
       <c r="J64" s="1">
         <v>3</v>
@@ -4878,27 +4875,27 @@
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D65" s="1">
         <v>2</v>
       </c>
       <c r="E65" s="1"/>
       <c r="F65" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G65" s="1"/>
       <c r="H65" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="I65" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="I65" s="1" t="s">
-        <v>170</v>
       </c>
       <c r="J65" s="1">
         <v>9</v>
@@ -4928,27 +4925,27 @@
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D66" s="1">
         <v>1</v>
       </c>
       <c r="E66" s="1"/>
       <c r="F66" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G66" s="1"/>
       <c r="H66" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="I66" s="1" t="s">
         <v>172</v>
-      </c>
-      <c r="I66" s="1" t="s">
-        <v>173</v>
       </c>
       <c r="J66" s="1">
         <v>4</v>
@@ -4975,32 +4972,32 @@
         <v>0</v>
       </c>
       <c r="T66" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D67" s="1">
         <v>2</v>
       </c>
       <c r="E67" s="1"/>
       <c r="F67" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G67" s="1"/>
       <c r="H67" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J67" s="1">
         <v>1</v>
@@ -5027,32 +5024,32 @@
         <v>0</v>
       </c>
       <c r="T67" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D68" s="1">
         <v>3</v>
       </c>
       <c r="E68" s="1"/>
       <c r="F68" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G68" s="1"/>
       <c r="H68" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I68" s="1" t="s">
         <v>177</v>
-      </c>
-      <c r="I68" s="1" t="s">
-        <v>178</v>
       </c>
       <c r="J68" s="1">
         <v>8</v>
@@ -5079,32 +5076,32 @@
         <v>0</v>
       </c>
       <c r="T68" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D69" s="1">
         <v>1</v>
       </c>
       <c r="E69" s="1"/>
       <c r="F69" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G69" s="1"/>
       <c r="H69" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="I69" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="I69" s="1" t="s">
-        <v>141</v>
       </c>
       <c r="J69" s="1">
         <v>12</v>
@@ -5134,27 +5131,27 @@
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D70" s="1">
         <v>2</v>
       </c>
       <c r="E70" s="1"/>
       <c r="F70" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G70" s="1"/>
       <c r="H70" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="I70" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="I70" s="1" t="s">
-        <v>141</v>
       </c>
       <c r="J70" s="1">
         <v>12</v>
@@ -5184,27 +5181,27 @@
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D71" s="1">
         <v>1</v>
       </c>
       <c r="E71" s="1"/>
       <c r="F71" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G71" s="1"/>
       <c r="H71" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J71" s="1">
         <v>6</v>
@@ -5234,27 +5231,27 @@
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D72" s="1">
         <v>2</v>
       </c>
       <c r="E72" s="1"/>
       <c r="F72" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G72" s="1"/>
       <c r="H72" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J72" s="1">
         <v>3</v>
@@ -5281,32 +5278,32 @@
         <v>0</v>
       </c>
       <c r="T72" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D73" s="1">
         <v>3</v>
       </c>
       <c r="E73" s="1"/>
       <c r="F73" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G73" s="1"/>
       <c r="H73" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J73" s="1">
         <v>3</v>
@@ -5336,27 +5333,27 @@
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D74" s="1">
         <v>4</v>
       </c>
       <c r="E74" s="1"/>
       <c r="F74" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G74" s="1"/>
       <c r="H74" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="I74" s="1" t="s">
         <v>189</v>
-      </c>
-      <c r="I74" s="1" t="s">
-        <v>190</v>
       </c>
       <c r="J74" s="1">
         <v>2</v>
@@ -5386,27 +5383,27 @@
     </row>
     <row r="75" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D75" s="1">
         <v>5</v>
       </c>
       <c r="E75" s="1"/>
       <c r="F75" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G75" s="1"/>
       <c r="H75" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J75" s="1">
         <v>9</v>
@@ -5433,32 +5430,32 @@
         <v>0</v>
       </c>
       <c r="T75" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D76" s="1">
         <v>6</v>
       </c>
       <c r="E76" s="1"/>
       <c r="F76" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G76" s="1"/>
       <c r="H76" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J76" s="1">
         <v>3</v>
@@ -5488,27 +5485,27 @@
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D77" s="1">
         <v>7</v>
       </c>
       <c r="E77" s="1"/>
       <c r="F77" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G77" s="1"/>
       <c r="H77" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J77" s="1">
         <v>3</v>
@@ -5538,27 +5535,27 @@
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D78" s="1">
         <v>8</v>
       </c>
       <c r="E78" s="1"/>
       <c r="F78" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G78" s="1"/>
       <c r="H78" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J78" s="1">
         <v>10</v>
@@ -5585,32 +5582,32 @@
         <v>0</v>
       </c>
       <c r="T78" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D79" s="4">
         <v>1</v>
       </c>
       <c r="E79" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="F79" s="4" t="s">
         <v>241</v>
-      </c>
-      <c r="F79" s="4" t="s">
-        <v>242</v>
       </c>
       <c r="G79" s="4"/>
       <c r="H79" s="4"/>
       <c r="I79" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J79" s="4"/>
       <c r="K79" s="4"/>
@@ -5638,27 +5635,27 @@
     </row>
     <row r="80" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D80" s="4">
         <v>2</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G80" s="4"/>
       <c r="H80" s="4"/>
       <c r="I80" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="J80" s="4"/>
       <c r="K80" s="4"/>
@@ -5686,27 +5683,27 @@
     </row>
     <row r="81" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D81" s="4">
         <v>3</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G81" s="4"/>
       <c r="H81" s="4"/>
       <c r="I81" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J81" s="4"/>
       <c r="K81" s="4"/>
@@ -5734,27 +5731,27 @@
     </row>
     <row r="82" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D82" s="4">
         <v>1</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G82" s="4"/>
       <c r="H82" s="4"/>
       <c r="I82" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J82" s="4"/>
       <c r="K82" s="4"/>
@@ -5782,27 +5779,27 @@
     </row>
     <row r="83" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D83" s="4">
         <v>2</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G83" s="4"/>
       <c r="H83" s="4"/>
       <c r="I83" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J83" s="4"/>
       <c r="K83" s="4"/>
@@ -5830,27 +5827,27 @@
     </row>
     <row r="84" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D84" s="4">
         <v>3</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G84" s="4"/>
       <c r="H84" s="4"/>
       <c r="I84" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J84" s="4"/>
       <c r="K84" s="4"/>
@@ -5878,27 +5875,27 @@
     </row>
     <row r="85" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D85" s="4">
         <v>1</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G85" s="4"/>
       <c r="H85" s="4"/>
       <c r="I85" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J85" s="4"/>
       <c r="K85" s="4"/>
@@ -5926,27 +5923,27 @@
     </row>
     <row r="86" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D86" s="4">
         <v>2</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G86" s="4"/>
       <c r="H86" s="4"/>
       <c r="I86" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="J86" s="4"/>
       <c r="K86" s="4"/>
@@ -5974,27 +5971,27 @@
     </row>
     <row r="87" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D87" s="4">
         <v>3</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G87" s="4"/>
       <c r="H87" s="4"/>
       <c r="I87" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J87" s="4"/>
       <c r="K87" s="4"/>
@@ -6022,27 +6019,27 @@
     </row>
     <row r="88" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D88" s="4">
         <v>4</v>
       </c>
       <c r="E88" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="F88" s="4" t="s">
         <v>246</v>
-      </c>
-      <c r="F88" s="4" t="s">
-        <v>247</v>
       </c>
       <c r="G88" s="4"/>
       <c r="H88" s="4"/>
       <c r="I88" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J88" s="4"/>
       <c r="K88" s="4"/>
@@ -6070,27 +6067,27 @@
     </row>
     <row r="89" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D89" s="4">
         <v>5</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G89" s="4"/>
       <c r="H89" s="4"/>
       <c r="I89" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J89" s="4"/>
       <c r="K89" s="4"/>
@@ -6118,27 +6115,27 @@
     </row>
     <row r="90" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D90" s="4">
         <v>6</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G90" s="4"/>
       <c r="H90" s="4"/>
       <c r="I90" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J90" s="4"/>
       <c r="K90" s="4"/>
@@ -6166,27 +6163,27 @@
     </row>
     <row r="91" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D91" s="4">
         <v>7</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G91" s="4"/>
       <c r="H91" s="4"/>
       <c r="I91" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J91" s="4"/>
       <c r="K91" s="4"/>
@@ -6214,27 +6211,27 @@
     </row>
     <row r="92" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D92" s="4">
         <v>1</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G92" s="4"/>
       <c r="H92" s="4"/>
       <c r="I92" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J92" s="4"/>
       <c r="K92" s="4"/>
@@ -6262,27 +6259,27 @@
     </row>
     <row r="93" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D93" s="4">
         <v>2</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G93" s="4"/>
       <c r="H93" s="4"/>
       <c r="I93" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J93" s="4"/>
       <c r="K93" s="4"/>
@@ -6310,27 +6307,27 @@
     </row>
     <row r="94" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D94" s="4">
         <v>3</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G94" s="4"/>
       <c r="H94" s="4"/>
       <c r="I94" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J94" s="4"/>
       <c r="K94" s="4"/>
@@ -6358,27 +6355,27 @@
     </row>
     <row r="95" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D95" s="4">
         <v>1</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G95" s="4"/>
       <c r="H95" s="4"/>
       <c r="I95" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J95" s="4"/>
       <c r="K95" s="4"/>
@@ -6406,27 +6403,27 @@
     </row>
     <row r="96" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D96" s="4">
         <v>2</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G96" s="4"/>
       <c r="H96" s="4"/>
       <c r="I96" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="J96" s="4"/>
       <c r="K96" s="4"/>
@@ -6454,27 +6451,27 @@
     </row>
     <row r="97" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D97" s="4">
         <v>3</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G97" s="4"/>
       <c r="H97" s="4"/>
       <c r="I97" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J97" s="4"/>
       <c r="K97" s="4"/>
@@ -6502,27 +6499,27 @@
     </row>
     <row r="98" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D98" s="4">
         <v>1</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G98" s="4"/>
       <c r="H98" s="4"/>
       <c r="I98" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J98" s="4"/>
       <c r="K98" s="4"/>
@@ -6550,27 +6547,27 @@
     </row>
     <row r="99" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D99" s="4">
         <v>2</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G99" s="4"/>
       <c r="H99" s="4"/>
       <c r="I99" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J99" s="4"/>
       <c r="K99" s="4"/>
@@ -6598,27 +6595,27 @@
     </row>
     <row r="100" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D100" s="4">
         <v>3</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G100" s="4"/>
       <c r="H100" s="4"/>
       <c r="I100" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J100" s="4"/>
       <c r="K100" s="4"/>
@@ -6646,27 +6643,27 @@
     </row>
     <row r="101" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D101" s="4">
         <v>4</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G101" s="4"/>
       <c r="H101" s="4"/>
       <c r="I101" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J101" s="4"/>
       <c r="K101" s="4"/>
@@ -6694,27 +6691,27 @@
     </row>
     <row r="102" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D102" s="1">
         <v>4</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G102" s="1"/>
       <c r="H102" s="1"/>
       <c r="I102" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J102" s="1"/>
       <c r="K102" s="1"/>
@@ -6742,27 +6739,27 @@
     </row>
     <row r="103" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C103" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D103" s="4">
+        <v>1</v>
+      </c>
+      <c r="E103" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="D103" s="4">
-        <v>1</v>
-      </c>
-      <c r="E103" s="4" t="s">
+      <c r="F103" s="4" t="s">
         <v>125</v>
-      </c>
-      <c r="F103" s="4" t="s">
-        <v>126</v>
       </c>
       <c r="G103" s="4"/>
       <c r="H103" s="4"/>
       <c r="I103" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J103" s="4"/>
       <c r="K103" s="4"/>
@@ -6791,27 +6788,27 @@
     </row>
     <row r="104" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D104" s="4">
         <v>2</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G104" s="4"/>
       <c r="H104" s="4"/>
       <c r="I104" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J104" s="4"/>
       <c r="K104" s="4"/>
@@ -6840,27 +6837,27 @@
     </row>
     <row r="105" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D105" s="4">
         <v>3</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G105" s="4"/>
       <c r="H105" s="4"/>
       <c r="I105" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="J105" s="4"/>
       <c r="K105" s="4"/>
@@ -6889,27 +6886,27 @@
     </row>
     <row r="106" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D106" s="4">
         <v>4</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G106" s="4"/>
       <c r="H106" s="4"/>
       <c r="I106" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="J106" s="4"/>
       <c r="K106" s="4"/>
@@ -6938,27 +6935,27 @@
     </row>
     <row r="107" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D107" s="4">
         <v>5</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G107" s="4"/>
       <c r="H107" s="4"/>
       <c r="I107" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J107" s="4"/>
       <c r="K107" s="4"/>
@@ -6987,27 +6984,27 @@
     </row>
     <row r="108" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D108" s="4">
         <v>6</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G108" s="4"/>
       <c r="H108" s="4"/>
       <c r="I108" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J108" s="4"/>
       <c r="K108" s="4"/>
@@ -7036,27 +7033,27 @@
     </row>
     <row r="109" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D109" s="4">
         <v>7</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G109" s="4"/>
       <c r="H109" s="4"/>
       <c r="I109" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J109" s="4"/>
       <c r="K109" s="4"/>
@@ -7085,27 +7082,27 @@
     </row>
     <row r="110" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D110" s="4">
         <v>8</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G110" s="4"/>
       <c r="H110" s="4"/>
       <c r="I110" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J110" s="4"/>
       <c r="K110" s="4"/>
@@ -7134,27 +7131,27 @@
     </row>
     <row r="111" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D111" s="4">
         <v>9</v>
       </c>
       <c r="E111" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="F111" s="4" t="s">
         <v>133</v>
-      </c>
-      <c r="F111" s="4" t="s">
-        <v>134</v>
       </c>
       <c r="G111" s="4"/>
       <c r="H111" s="4"/>
       <c r="I111" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J111" s="4"/>
       <c r="K111" s="4"/>
@@ -7183,25 +7180,25 @@
     </row>
     <row r="112" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D112" s="4">
         <v>10</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F112" s="4"/>
       <c r="G112" s="4"/>
       <c r="H112" s="4"/>
       <c r="I112" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J112" s="4"/>
       <c r="K112" s="4"/>
@@ -7230,25 +7227,25 @@
     </row>
     <row r="113" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D113" s="4">
         <v>11</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F113" s="4"/>
       <c r="G113" s="4"/>
       <c r="H113" s="4"/>
       <c r="I113" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J113" s="4"/>
       <c r="K113" s="4"/>
@@ -7277,25 +7274,25 @@
     </row>
     <row r="114" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D114" s="4">
         <v>12</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F114" s="4"/>
       <c r="G114" s="4"/>
       <c r="H114" s="4"/>
       <c r="I114" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J114" s="4"/>
       <c r="K114" s="4"/>
@@ -7324,27 +7321,27 @@
     </row>
     <row r="115" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D115" s="4">
         <v>13</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G115" s="4"/>
       <c r="H115" s="4"/>
       <c r="I115" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J115" s="4"/>
       <c r="K115" s="4"/>
@@ -7373,27 +7370,27 @@
     </row>
     <row r="116" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D116" s="4">
         <v>15</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G116" s="4"/>
       <c r="H116" s="4"/>
       <c r="I116" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J116" s="4"/>
       <c r="K116" s="4"/>
@@ -7422,27 +7419,27 @@
     </row>
     <row r="117" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D117" s="4">
         <v>16</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G117" s="4"/>
       <c r="H117" s="4"/>
       <c r="I117" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J117" s="4"/>
       <c r="K117" s="4"/>
@@ -7511,84 +7508,84 @@
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B1" t="s">
         <v>197</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>198</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>199</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>200</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>201</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>202</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>203</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>204</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
+        <v>276</v>
+      </c>
+      <c r="K1" t="s">
         <v>205</v>
       </c>
-      <c r="J1" t="s">
-        <v>277</v>
-      </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>206</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
+        <v>279</v>
+      </c>
+      <c r="N1" t="s">
         <v>207</v>
       </c>
-      <c r="M1" t="s">
-        <v>280</v>
-      </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>208</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>209</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>210</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>211</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>212</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>213</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>214</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>215</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>216</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>217</v>
-      </c>
-      <c r="X1" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2">
         <v>12</v>
@@ -7606,14 +7603,14 @@
         <v>0.88</v>
       </c>
       <c r="H2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I2">
         <f>((D2*60*8*G2*2)/(E2*36*840*C2*2.202))*3</f>
         <v>3.358291545501034</v>
       </c>
       <c r="J2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="K2">
         <f>L2*30</f>
@@ -7623,14 +7620,14 @@
         <v>9386.496000000001</v>
       </c>
       <c r="M2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N2">
         <f t="shared" ref="N2:N18" si="0">L2/I2</f>
         <v>2795.0211805090912</v>
       </c>
       <c r="O2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P2" s="5">
         <f>N2/240</f>
@@ -7643,21 +7640,21 @@
         <v>0.85</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="T2">
         <f t="shared" ref="T2:T19" si="1">Q2*R2*8*60*1.09/(C2*840*2.202)*3</f>
         <v>51.091540158297647</v>
       </c>
       <c r="U2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="V2" s="3">
         <f>L2/T2</f>
         <v>183.71918268499417</v>
       </c>
       <c r="W2" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="X2">
         <f>V2/72</f>
@@ -7666,10 +7663,10 @@
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3">
         <v>12</v>
@@ -7702,7 +7699,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P3" s="5">
         <f t="shared" ref="P3:P18" si="4">N3/240</f>
@@ -7723,10 +7720,10 @@
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>222</v>
+      </c>
+      <c r="B4" t="s">
         <v>223</v>
-      </c>
-      <c r="B4" t="s">
-        <v>224</v>
       </c>
       <c r="C4">
         <v>15</v>
@@ -7759,7 +7756,7 @@
         <v>596.83007999999995</v>
       </c>
       <c r="O4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P4" s="5">
         <f t="shared" si="4"/>
@@ -7788,10 +7785,10 @@
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5">
         <v>10</v>
@@ -7824,7 +7821,7 @@
         <v>3180.5991724137934</v>
       </c>
       <c r="O5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P5" s="5">
         <f t="shared" si="4"/>
@@ -7853,10 +7850,10 @@
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C6">
         <v>10</v>
@@ -7889,7 +7886,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P6" s="5">
         <f t="shared" si="4"/>
@@ -7918,10 +7915,10 @@
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B7" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -7954,7 +7951,7 @@
         <v>247.05990791999994</v>
       </c>
       <c r="O7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P7" s="5">
         <f t="shared" si="4"/>
@@ -7983,10 +7980,10 @@
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8">
         <v>4.5</v>
@@ -8019,7 +8016,7 @@
         <v>744.14360475000001</v>
       </c>
       <c r="O8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P8" s="5">
         <f t="shared" si="4"/>
@@ -8048,10 +8045,10 @@
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>228</v>
+      </c>
+      <c r="B9" t="s">
         <v>229</v>
-      </c>
-      <c r="B9" t="s">
-        <v>230</v>
       </c>
       <c r="C9">
         <v>3</v>
@@ -8084,7 +8081,7 @@
         <v>0</v>
       </c>
       <c r="O9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P9" s="5">
         <f t="shared" si="4"/>
@@ -8113,10 +8110,10 @@
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>228</v>
+      </c>
+      <c r="B10" t="s">
         <v>229</v>
-      </c>
-      <c r="B10" t="s">
-        <v>230</v>
       </c>
       <c r="C10">
         <v>3</v>
@@ -8149,7 +8146,7 @@
         <v>0</v>
       </c>
       <c r="O10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P10" s="5">
         <f t="shared" si="4"/>
@@ -8178,10 +8175,10 @@
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C11">
         <v>9.5</v>
@@ -8214,7 +8211,7 @@
         <v>0</v>
       </c>
       <c r="O11" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P11" s="5">
         <f t="shared" si="4"/>
@@ -8243,10 +8240,10 @@
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12">
         <v>8.0898876404494384</v>
@@ -8279,7 +8276,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P12" s="5">
         <f t="shared" si="4"/>
@@ -8308,10 +8305,10 @@
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13">
         <v>13.333333333333334</v>
@@ -8344,7 +8341,7 @@
         <v>1579.7083235294119</v>
       </c>
       <c r="O13" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P13" s="5">
         <f t="shared" si="4"/>
@@ -8373,10 +8370,10 @@
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C14">
         <v>13.333333333333334</v>
@@ -8409,7 +8406,7 @@
         <v>3487.5459500000002</v>
       </c>
       <c r="O14" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P14" s="5">
         <f t="shared" si="4"/>
@@ -8438,10 +8435,10 @@
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C15">
         <v>11.182795698924732</v>
@@ -8474,7 +8471,7 @@
         <v>1340.5441730550285</v>
       </c>
       <c r="O15" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P15" s="5">
         <f t="shared" si="4"/>
@@ -8503,10 +8500,10 @@
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C16">
         <v>11.182795698924732</v>
@@ -8539,7 +8536,7 @@
         <v>1914.8120308665402</v>
       </c>
       <c r="O16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P16" s="5">
         <f t="shared" si="4"/>
@@ -8568,10 +8565,10 @@
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C17">
         <v>11.182795698924732</v>
@@ -8604,7 +8601,7 @@
         <v>0</v>
       </c>
       <c r="O17" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P17" s="5">
         <f t="shared" si="4"/>
@@ -8633,10 +8630,10 @@
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18">
         <v>11.182795698924732</v>
@@ -8669,7 +8666,7 @@
         <v>0</v>
       </c>
       <c r="O18" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P18" s="5">
         <f t="shared" si="4"/>
@@ -8698,10 +8695,10 @@
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B19" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C19">
         <v>0.75</v>
@@ -8730,14 +8727,14 @@
         <v>2713.7828571428577</v>
       </c>
       <c r="M19" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N19">
         <f>L19/I19</f>
         <v>94.118060160000013</v>
       </c>
       <c r="O19" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P19" s="5">
         <f>N19/80</f>
@@ -8772,72 +8769,72 @@
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D22" t="s">
+        <v>2</v>
+      </c>
+      <c r="E22" t="s">
+        <v>285</v>
+      </c>
+      <c r="F22" t="s">
         <v>3</v>
       </c>
-      <c r="E22" t="s">
-        <v>2</v>
-      </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>4</v>
       </c>
-      <c r="G22" t="s">
+      <c r="H22" t="s">
+        <v>44</v>
+      </c>
+      <c r="I22" t="s">
+        <v>45</v>
+      </c>
+      <c r="J22" t="s">
+        <v>270</v>
+      </c>
+      <c r="K22" t="s">
+        <v>269</v>
+      </c>
+      <c r="L22" t="s">
         <v>5</v>
       </c>
-      <c r="H22" t="s">
-        <v>45</v>
-      </c>
-      <c r="I22" t="s">
-        <v>46</v>
-      </c>
-      <c r="J22" t="s">
-        <v>271</v>
-      </c>
-      <c r="K22" t="s">
-        <v>270</v>
-      </c>
-      <c r="L22" t="s">
+      <c r="M22" t="s">
         <v>6</v>
       </c>
-      <c r="M22" t="s">
+      <c r="N22" t="s">
         <v>7</v>
       </c>
-      <c r="N22" t="s">
+      <c r="O22" t="s">
         <v>8</v>
       </c>
-      <c r="O22" t="s">
+      <c r="P22" t="s">
         <v>9</v>
       </c>
-      <c r="P22" t="s">
+      <c r="Q22" t="s">
         <v>10</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C23" t="s">
+        <v>123</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23" t="s">
         <v>124</v>
       </c>
-      <c r="D23">
-        <v>1</v>
-      </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>125</v>
       </c>
-      <c r="F23" t="s">
-        <v>126</v>
-      </c>
       <c r="I23" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J23">
         <v>62</v>
@@ -8864,25 +8861,25 @@
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C24" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D24">
         <v>2</v>
       </c>
       <c r="E24" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F24" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I24" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J24">
         <v>2</v>
@@ -8909,25 +8906,25 @@
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C25" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D25">
         <v>3</v>
       </c>
       <c r="E25" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F25" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I25" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="J25">
         <v>33</v>
@@ -8954,25 +8951,25 @@
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C26" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D26">
         <v>4</v>
       </c>
       <c r="E26" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F26" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I26" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="J26">
         <v>51</v>
@@ -8999,25 +8996,25 @@
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C27" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D27">
         <v>5</v>
       </c>
       <c r="E27" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F27" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I27" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J27">
         <v>6</v>
@@ -9044,25 +9041,25 @@
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C28" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D28">
         <v>6</v>
       </c>
       <c r="E28" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F28" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I28" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J28">
         <v>6</v>
@@ -9089,25 +9086,25 @@
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C29" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D29">
         <v>7</v>
       </c>
       <c r="E29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I29" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J29">
         <v>3</v>
@@ -9134,25 +9131,25 @@
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D30">
         <v>8</v>
       </c>
       <c r="E30" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F30" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I30" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J30">
         <v>3</v>
@@ -9179,25 +9176,25 @@
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C31" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D31">
         <v>9</v>
       </c>
       <c r="E31" t="s">
+        <v>132</v>
+      </c>
+      <c r="F31" t="s">
         <v>133</v>
       </c>
-      <c r="F31" t="s">
-        <v>134</v>
-      </c>
       <c r="I31" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J31">
         <v>6</v>
@@ -9224,22 +9221,22 @@
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C32" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D32">
         <v>10</v>
       </c>
       <c r="E32" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I32" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J32">
         <v>3</v>
@@ -9266,22 +9263,22 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C33" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D33">
         <v>11</v>
       </c>
       <c r="E33" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I33" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J33">
         <v>1</v>
@@ -9308,22 +9305,22 @@
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C34" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D34">
         <v>12</v>
       </c>
       <c r="E34" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I34" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J34">
         <v>12</v>
@@ -9350,25 +9347,25 @@
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C35" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D35">
         <v>13</v>
       </c>
       <c r="E35" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F35" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I35" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -9395,25 +9392,25 @@
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C36" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D36">
         <v>15</v>
       </c>
       <c r="E36" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F36" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I36" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J36">
         <v>1</v>
@@ -9440,25 +9437,25 @@
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B37" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C37" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D37">
         <v>16</v>
       </c>
       <c r="E37" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F37" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I37" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J37">
         <v>6</v>
